--- a/CHECKLIST.xlsx
+++ b/CHECKLIST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE6DB8C-6164-4CD2-A462-70BF7CBF23CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00396C70-8FC0-4EF4-A96E-8A97A802D9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="230">
   <si>
     <t>Funzionalità</t>
   </si>
@@ -499,12 +499,6 @@
   </si>
   <si>
     <t>Line chart peso, volume, PR timeline (es. Chart.js o ECharts)</t>
-  </si>
-  <si>
-    <t>Export / Import dati</t>
-  </si>
-  <si>
-    <t>JSON completo + CSV, già implementato su mobile</t>
   </si>
   <si>
     <t>Dettaglio sessione da Calendario</t>
@@ -915,23 +909,11 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -940,6 +922,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1340,16 +1334,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1365,10 +1359,10 @@
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1376,16 +1370,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1393,10 +1387,10 @@
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1404,16 +1398,16 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1421,7 +1415,7 @@
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1432,16 +1426,16 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1449,10 +1443,10 @@
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1460,16 +1454,16 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="B10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1477,10 +1471,10 @@
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1488,16 +1482,16 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="B12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1505,10 +1499,10 @@
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1516,16 +1510,16 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1541,10 +1535,10 @@
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1552,16 +1546,16 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="B17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1569,10 +1563,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1580,16 +1574,16 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="20" t="s">
+      <c r="B19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1597,10 +1591,10 @@
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="B20" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -1608,16 +1602,16 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="20" t="s">
+      <c r="B21" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1625,7 +1619,7 @@
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -1636,16 +1630,16 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="20" t="s">
+      <c r="B23" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1653,10 +1647,10 @@
       <c r="A24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -1664,16 +1658,16 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="20" t="s">
+      <c r="B25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1681,10 +1675,10 @@
       <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="B26" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -1692,16 +1686,16 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="20" t="s">
+      <c r="B27" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1709,10 +1703,10 @@
       <c r="A28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -1720,16 +1714,16 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="20" t="s">
+      <c r="B29" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1737,10 +1731,10 @@
       <c r="A30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -1748,16 +1742,16 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="20" t="s">
+      <c r="B31" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1773,10 +1767,10 @@
       <c r="A33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -1784,16 +1778,16 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="20" t="s">
+      <c r="B34" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1801,10 +1795,10 @@
       <c r="A35" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="19" t="s">
+      <c r="B35" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="5" t="s">
@@ -1812,16 +1806,16 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="20" t="s">
+      <c r="B36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1829,10 +1823,10 @@
       <c r="A37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -1840,16 +1834,16 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="20" t="s">
+      <c r="B38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1857,10 +1851,10 @@
       <c r="A39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="5" t="s">
@@ -1868,16 +1862,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="20" t="s">
+      <c r="B40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1885,10 +1879,10 @@
       <c r="A41" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="19" t="s">
+      <c r="B41" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -1896,16 +1890,16 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="20" t="s">
+      <c r="B42" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1913,10 +1907,10 @@
       <c r="A43" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="19" t="s">
+      <c r="B43" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -1924,16 +1918,16 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="20" t="s">
+      <c r="B44" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1941,10 +1935,10 @@
       <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="19" t="s">
+      <c r="B45" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="5" t="s">
@@ -1952,16 +1946,16 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1969,10 +1963,10 @@
       <c r="A47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="19" t="s">
+      <c r="B47" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="5" t="s">
@@ -1980,16 +1974,16 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="20" t="s">
+      <c r="B48" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1997,10 +1991,10 @@
       <c r="A49" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="19" t="s">
+      <c r="B49" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="5" t="s">
@@ -2008,16 +2002,16 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="20" t="s">
+      <c r="B50" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2025,10 +2019,10 @@
       <c r="A51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="19" t="s">
+      <c r="B51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D51" s="5" t="s">
@@ -2036,16 +2030,16 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="20" t="s">
+      <c r="B52" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2053,7 +2047,7 @@
       <c r="A53" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -2064,16 +2058,16 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2081,7 +2075,7 @@
       <c r="A55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -2103,10 +2097,10 @@
       <c r="A57" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="19" t="s">
+      <c r="B57" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -2114,16 +2108,16 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="20" t="s">
+      <c r="B58" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2131,10 +2125,10 @@
       <c r="A59" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="19" t="s">
+      <c r="B59" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -2142,16 +2136,16 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="20" t="s">
+      <c r="B60" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2159,10 +2153,10 @@
       <c r="A61" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="19" t="s">
+      <c r="B61" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="5" t="s">
@@ -2170,16 +2164,16 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2195,10 +2189,10 @@
       <c r="A64" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B64" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="19" t="s">
+      <c r="B64" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -2206,16 +2200,16 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="21" t="s">
+      <c r="A65" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="20" t="s">
+      <c r="B65" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2223,10 +2217,10 @@
       <c r="A66" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="19" t="s">
+      <c r="B66" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -2234,16 +2228,16 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="21" t="s">
+      <c r="A67" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B67" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="20" t="s">
+      <c r="B67" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2251,10 +2245,10 @@
       <c r="A68" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="19" t="s">
+      <c r="B68" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2262,16 +2256,16 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B69" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="20" t="s">
+      <c r="B69" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2279,10 +2273,10 @@
       <c r="A70" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="19" t="s">
+      <c r="B70" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -2301,10 +2295,10 @@
       <c r="A72" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="19" t="s">
+      <c r="B72" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -2312,16 +2306,16 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B73" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="20" t="s">
+      <c r="B73" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2329,10 +2323,10 @@
       <c r="A74" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B74" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="19" t="s">
+      <c r="B74" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -2340,16 +2334,16 @@
       </c>
     </row>
     <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B75" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="20" t="s">
+      <c r="B75" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2365,10 +2359,10 @@
       <c r="A77" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="19" t="s">
+      <c r="B77" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -2376,16 +2370,16 @@
       </c>
     </row>
     <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="20" t="s">
+      <c r="B78" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2393,10 +2387,10 @@
       <c r="A79" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B79" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="19" t="s">
+      <c r="B79" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -2404,7 +2398,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -2413,7 +2407,7 @@
       <c r="C80" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D80" s="20" t="s">
+      <c r="D80" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2429,10 +2423,10 @@
       <c r="A82" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="19" t="s">
+      <c r="B82" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -2440,16 +2434,16 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="21" t="s">
+      <c r="A83" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="20" t="s">
+      <c r="B83" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2457,10 +2451,10 @@
       <c r="A84" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="19" t="s">
+      <c r="B84" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -2468,16 +2462,16 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="21" t="s">
+      <c r="A85" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B85" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="20" t="s">
+      <c r="B85" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2485,10 +2479,10 @@
       <c r="A86" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B86" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="19" t="s">
+      <c r="B86" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -2496,16 +2490,16 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="21" t="s">
+      <c r="A87" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D87" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2521,10 +2515,10 @@
       <c r="A89" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="19" t="s">
+      <c r="B89" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="5" t="s">
@@ -2532,16 +2526,16 @@
       </c>
     </row>
     <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="20" t="s">
+      <c r="B90" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2549,10 +2543,10 @@
       <c r="A91" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="19" t="s">
+      <c r="B91" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D91" s="5" t="s">
@@ -2560,16 +2554,16 @@
       </c>
     </row>
     <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="21" t="s">
+      <c r="A92" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" s="20" t="s">
+      <c r="B92" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2577,7 +2571,7 @@
       <c r="A93" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="8" t="s">
@@ -2588,16 +2582,16 @@
       </c>
     </row>
     <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="B94" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D94" s="20" t="s">
+      <c r="D94" s="16" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2605,7 +2599,7 @@
       <c r="A95" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
@@ -2616,16 +2610,16 @@
       </c>
     </row>
     <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D96" s="20" t="s">
+      <c r="B96" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2641,10 +2635,10 @@
       <c r="A98" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="19" t="s">
+      <c r="B98" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -2652,16 +2646,16 @@
       </c>
     </row>
     <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="21" t="s">
+      <c r="A99" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B99" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D99" s="20" t="s">
+      <c r="B99" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2669,10 +2663,10 @@
       <c r="A100" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="19" t="s">
+      <c r="B100" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -2680,16 +2674,16 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="21" t="s">
+      <c r="A101" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B101" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" s="20" t="s">
+      <c r="B101" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2697,7 +2691,7 @@
       <c r="A102" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B102" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="8" t="s">
@@ -2719,10 +2713,10 @@
       <c r="A104" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B104" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="19" t="s">
+      <c r="B104" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -2730,16 +2724,16 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="21" t="s">
+      <c r="A105" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B105" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D105" s="20" t="s">
+      <c r="B105" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2747,10 +2741,10 @@
       <c r="A106" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="19" t="s">
+      <c r="B106" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -2758,16 +2752,16 @@
       </c>
     </row>
     <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="21" t="s">
+      <c r="A107" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B107" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D107" s="20" t="s">
+      <c r="B107" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2775,7 +2769,7 @@
       <c r="A108" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="7" t="s">
@@ -2786,16 +2780,16 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="21" t="s">
+      <c r="A109" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B109" s="19" t="s">
+      <c r="B109" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D109" s="20" t="s">
+      <c r="D109" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2803,7 +2797,7 @@
       <c r="A110" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B110" s="19" t="s">
+      <c r="B110" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -2814,16 +2808,16 @@
       </c>
     </row>
     <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="21" t="s">
+      <c r="A111" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D111" s="20" t="s">
+      <c r="D111" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2853,10 +2847,10 @@
       <c r="A114" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B114" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="19" t="s">
+      <c r="B114" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -2864,16 +2858,16 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="21" t="s">
+      <c r="A115" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B115" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D115" s="20" t="s">
+      <c r="B115" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2881,10 +2875,10 @@
       <c r="A116" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B116" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="19" t="s">
+      <c r="B116" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -2892,16 +2886,16 @@
       </c>
     </row>
     <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D117" s="20" t="s">
+      <c r="D117" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2909,10 +2903,10 @@
       <c r="A118" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="19" t="s">
+      <c r="B118" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -2920,16 +2914,16 @@
       </c>
     </row>
     <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B119" s="19" t="s">
+      <c r="B119" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D119" s="20" t="s">
+      <c r="D119" s="16" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2945,10 +2939,10 @@
       <c r="A121" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B121" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" s="19" t="s">
+      <c r="B121" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -2956,16 +2950,16 @@
       </c>
     </row>
     <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B122" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D122" s="20" t="s">
+      <c r="B122" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2973,10 +2967,10 @@
       <c r="A123" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B123" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="19" t="s">
+      <c r="B123" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="5" t="s">
@@ -2984,16 +2978,16 @@
       </c>
     </row>
     <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B124" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D124" s="20" t="s">
+      <c r="B124" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3001,27 +2995,27 @@
       <c r="A125" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B125" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>7</v>
+      <c r="B125" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B126" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="20" t="s">
+      <c r="B126" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3029,27 +3023,27 @@
       <c r="A127" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B127" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>7</v>
+      <c r="B127" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B128" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D128" s="20" t="s">
+      <c r="B128" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3057,10 +3051,10 @@
       <c r="A129" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B129" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="19" t="s">
+      <c r="B129" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D129" s="5" t="s">
@@ -3068,16 +3062,16 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B130" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C130" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D130" s="20" t="s">
+      <c r="B130" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3085,7 +3079,7 @@
       <c r="A131" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C131" s="7" t="s">
@@ -3096,16 +3090,16 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B132" s="19" t="s">
+      <c r="B132" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D132" s="20" t="s">
+      <c r="D132" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3121,10 +3115,10 @@
       <c r="A134" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B134" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C134" s="19" t="s">
+      <c r="B134" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -3132,16 +3126,16 @@
       </c>
     </row>
     <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B135" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" s="20" t="s">
+      <c r="B135" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3149,10 +3143,10 @@
       <c r="A136" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B136" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C136" s="19" t="s">
+      <c r="B136" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -3160,16 +3154,16 @@
       </c>
     </row>
     <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="21" t="s">
+      <c r="A137" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B137" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D137" s="20" t="s">
+      <c r="B137" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3177,10 +3171,10 @@
       <c r="A138" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B138" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C138" s="19" t="s">
+      <c r="B138" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -3199,7 +3193,7 @@
       <c r="A140" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B140" s="19" t="s">
+      <c r="B140" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C140" s="7" t="s">
@@ -3210,16 +3204,16 @@
       </c>
     </row>
     <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B141" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D141" s="20" t="s">
+      <c r="B141" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3227,10 +3221,10 @@
       <c r="A142" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B142" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C142" s="19" t="s">
+      <c r="B142" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -3238,39 +3232,39 @@
       </c>
     </row>
     <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="21" t="s">
+      <c r="A143" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B143" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143" s="20" t="s">
+      <c r="B143" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A103:D103"/>
     <mergeCell ref="A113:D113"/>
     <mergeCell ref="A120:D120"/>
     <mergeCell ref="A133:D133"/>
     <mergeCell ref="A139:D139"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A63:D63"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B89:C96 B82:C87 B77:C80 B72:C75 B64:C70 B57:C62 B33:C55 B3:C14 B16:C31 B140:C143 B134:C138 B121:C132 B114:C119 B104:C112 B98:C102" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B89:C96 B82:C87 B77:C80 B72:C75 B64:C70 B57:C62 B33:C55 B3:C14 B16:C31 B140:C143 B134:C138 B98:C102 B114:C119 B104:C112 B121:C132" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"✓,~,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3323,7 +3317,7 @@
   <sheetPr>
     <tabColor rgb="FFFBBF24"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3351,13 +3345,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -3380,16 +3374,16 @@
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3397,16 +3391,16 @@
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3414,16 +3408,16 @@
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3431,16 +3425,16 @@
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3448,16 +3442,16 @@
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3465,16 +3459,16 @@
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3482,59 +3476,59 @@
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="C12" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="D12" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>181</v>
       </c>
     </row>
@@ -3542,16 +3536,16 @@
       <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>183</v>
       </c>
     </row>
@@ -3559,16 +3553,16 @@
       <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>185</v>
       </c>
     </row>
@@ -3576,16 +3570,16 @@
       <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3593,16 +3587,16 @@
       <c r="A17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>189</v>
       </c>
     </row>
@@ -3610,16 +3604,16 @@
       <c r="A18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3627,16 +3621,16 @@
       <c r="A19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3644,16 +3638,16 @@
       <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3661,16 +3655,16 @@
       <c r="A21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3678,16 +3672,16 @@
       <c r="A22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="B22" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3695,16 +3689,16 @@
       <c r="A23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3712,16 +3706,16 @@
       <c r="A24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="B24" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3729,16 +3723,16 @@
       <c r="A25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3746,59 +3740,59 @@
       <c r="A26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+    </row>
+    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="E28" s="5" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>213</v>
       </c>
     </row>
@@ -3806,16 +3800,16 @@
       <c r="A30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>215</v>
       </c>
     </row>
@@ -3823,16 +3817,16 @@
       <c r="A31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="D31" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>217</v>
       </c>
     </row>
@@ -3840,16 +3834,16 @@
       <c r="A32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="B32" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3857,16 +3851,16 @@
       <c r="A33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="D33" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3874,16 +3868,16 @@
       <c r="A34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="12" t="s">
+      <c r="B34" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>223</v>
       </c>
     </row>
@@ -3891,16 +3885,16 @@
       <c r="A35" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="D35" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>225</v>
       </c>
     </row>
@@ -3908,16 +3902,16 @@
       <c r="A36" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="B36" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3925,44 +3919,27 @@
       <c r="A37" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="D37" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>229</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="A3:A11 A29:A38 A13:A27" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A28:A37 A12:A26 A3:A10" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"✓,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3987,7 +3964,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A2:A200</xm:sqref>
+          <xm:sqref>A2:A199</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
